--- a/scripts/xlsx2json/translations.xlsx
+++ b/scripts/xlsx2json/translations.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
   <si>
     <t>key</t>
   </si>
@@ -177,6 +177,66 @@
   </si>
   <si>
     <t>Cerrar notificación</t>
+  </si>
+  <si>
+    <t>message.error_1200</t>
+  </si>
+  <si>
+    <t>账号或密码错误。</t>
+  </si>
+  <si>
+    <t>Incorrect username or password.</t>
+  </si>
+  <si>
+    <t>Nome de usuário ou senha incorretos.</t>
+  </si>
+  <si>
+    <t>Nombre de usuario o contraseña incorrectos.</t>
+  </si>
+  <si>
+    <t>message.error_1201</t>
+  </si>
+  <si>
+    <t>登录失败，请稍后再试。</t>
+  </si>
+  <si>
+    <t>Login failed. Please try again later.</t>
+  </si>
+  <si>
+    <t>Falha ao fazer login. Tente novamente mais tarde.</t>
+  </si>
+  <si>
+    <t>Error al iniciar sesión. Inténtalo de nuevo más tarde.</t>
+  </si>
+  <si>
+    <t>message.error_1202</t>
+  </si>
+  <si>
+    <t>用户名不存在。</t>
+  </si>
+  <si>
+    <t>Username does not exist.</t>
+  </si>
+  <si>
+    <t>O nome de usuário não existe.</t>
+  </si>
+  <si>
+    <t>El nombre de usuario no existe.</t>
+  </si>
+  <si>
+    <t>message.error_1203</t>
+  </si>
+  <si>
+    <t>您上一次的提款被拒絕。請等待 {{time}} 分鐘後再嘗試。</t>
+  </si>
+  <si>
+    <t>Your last withdrawal was decllined. Please wait {{time}} minutes before trying again.</t>
+  </si>
+  <si>
+    <t>Seu último saque foi rejeitado. Aguarde {{time}} minutos antes de tentar novamente.</t>
+  </si>
+  <si>
+    <t>Tu último retiro fue rechazado. Por favor espera {{time}} minutos antes de intentarlo de nuevo.</t>
   </si>
 </sst>
 </file>
@@ -189,10 +249,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -662,141 +729,165 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1332,189 +1423,282 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.8653846153846" customWidth="1"/>
-    <col min="2" max="2" width="44.2307692307692" customWidth="1"/>
-    <col min="3" max="3" width="65.7019230769231" customWidth="1"/>
-    <col min="4" max="4" width="50.6442307692308" customWidth="1"/>
-    <col min="5" max="5" width="51.2788461538462" customWidth="1"/>
+    <col min="1" max="1" width="19.8653846153846" style="1" customWidth="1"/>
+    <col min="2" max="2" width="55.5961538461538" style="1" customWidth="1"/>
+    <col min="3" max="3" width="65.7019230769231" style="1" customWidth="1"/>
+    <col min="4" max="4" width="50.6442307692308" style="1" customWidth="1"/>
+    <col min="5" max="5" width="51.2788461538462" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.23076923076923" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1" ht="17" spans="1:6">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+    <row r="3" ht="17" spans="1:6">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+    <row r="4" ht="17" spans="1:6">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+    <row r="5" ht="17" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+    <row r="6" ht="17" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+    <row r="7" ht="17" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+    <row r="8" ht="17" spans="1:6">
+      <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+    <row r="9" ht="17" spans="1:6">
+      <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="F9" s="2"/>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+    <row r="10" ht="17" spans="1:6">
+      <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="6" t="s">
         <v>49</v>
       </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" ht="17" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" ht="17" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" ht="17" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" ht="31" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="5"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="5"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/xlsx2json/translations.xlsx
+++ b/scripts/xlsx2json/translations.xlsx
@@ -227,7 +227,7 @@
     <t>message.error_1203</t>
   </si>
   <si>
-    <t>您上一次的提款被拒絕。請等待 {{time}} 分鐘後再嘗試。</t>
+    <t>您上一次的提款被拒绝。请等待 {{time}} 分钟后再尝试。</t>
   </si>
   <si>
     <t>Your last withdrawal was decllined. Please wait {{time}} minutes before trying again.</t>
@@ -859,7 +859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -869,19 +869,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1470,7 +1458,7 @@
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" ht="17" spans="1:6">
       <c r="A3" s="2" t="s">
@@ -1584,7 +1572,7 @@
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1602,16 +1590,16 @@
       <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F10" s="2"/>
@@ -1620,16 +1608,16 @@
       <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F11" s="2"/>
@@ -1638,16 +1626,16 @@
       <c r="A12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F12" s="2"/>
@@ -1656,16 +1644,16 @@
       <c r="A13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="2"/>
@@ -1677,28 +1665,28 @@
       <c r="B14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="4" t="s">
         <v>69</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="B15" s="5"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="B16" s="5"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/xlsx2json/translations.xlsx
+++ b/scripts/xlsx2json/translations.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
   <si>
     <t>key</t>
   </si>
@@ -237,6 +237,12 @@
   </si>
   <si>
     <t>Tu último retiro fue rechazado. Por favor espera {{time}} minutos antes de intentarlo de nuevo.</t>
+  </si>
+  <si>
+    <t>message.error_1204</t>
+  </si>
+  <si>
+    <t>余额不足，请充值。</t>
   </si>
 </sst>
 </file>
@@ -1676,8 +1682,13 @@
       </c>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:6">
-      <c r="B15" s="3"/>
+    <row r="15" ht="17" spans="1:6">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>

--- a/scripts/xlsx2json/translations.xlsx
+++ b/scripts/xlsx2json/translations.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29840" windowHeight="13100"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,10 +32,10 @@
     <t>key</t>
   </si>
   <si>
-    <t>zh-CN</t>
-  </si>
-  <si>
-    <t>en-US</t>
+    <t>zh</t>
+  </si>
+  <si>
+    <t>en</t>
   </si>
   <si>
     <t>pt</t>

--- a/scripts/xlsx2json/translations.xlsx
+++ b/scripts/xlsx2json/translations.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="30240" windowHeight="12320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
